--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1477,6 +1477,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -8224,7 +8228,7 @@
         <v>462</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>463</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8239,7 +8243,7 @@
         <v>453</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8247,10 +8251,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8276,10 +8280,10 @@
         <v>459</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8330,7 +8334,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8342,7 +8346,7 @@
         <v>462</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>463</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8357,7 +8361,7 @@
         <v>453</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>20</v>
@@ -8365,10 +8369,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8394,10 +8398,10 @@
         <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8427,10 +8431,10 @@
         <v>377</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8448,7 +8452,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8475,7 +8479,7 @@
         <v>453</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>20</v>
@@ -8483,10 +8487,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8512,16 +8516,16 @@
         <v>234</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8549,10 +8553,10 @@
         <v>240</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8570,7 +8574,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8591,10 +8595,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>392</v>
@@ -8605,10 +8609,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8634,16 +8638,16 @@
         <v>234</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8671,10 +8675,10 @@
         <v>406</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8692,7 +8696,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8713,10 +8717,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>392</v>
@@ -8727,10 +8731,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8753,17 +8757,17 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8812,7 +8816,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8839,7 +8843,7 @@
         <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>20</v>
@@ -8847,10 +8851,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8873,13 +8877,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8930,7 +8934,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8957,7 +8961,7 @@
         <v>453</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -8965,10 +8969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8991,16 +8995,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9050,7 +9054,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9074,7 +9078,7 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>200</v>
@@ -9085,10 +9089,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9111,16 +9115,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9170,7 +9174,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9194,10 +9198,10 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9205,10 +9209,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9234,16 +9238,16 @@
         <v>178</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9292,7 +9296,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9316,10 +9320,10 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>20</v>
@@ -9327,10 +9331,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9445,10 +9449,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9565,10 +9569,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9687,10 +9691,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9716,13 +9720,13 @@
         <v>234</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>250</v>
@@ -9753,10 +9757,10 @@
         <v>406</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9774,7 +9778,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>93</v>
@@ -9795,7 +9799,7 @@
         <v>254</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>256</v>
@@ -9809,10 +9813,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9835,16 +9839,16 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>316</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>318</v>
@@ -9896,7 +9900,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9917,7 +9921,7 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>321</v>
@@ -9931,10 +9935,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9960,13 +9964,13 @@
         <v>234</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>376</v>
@@ -10018,7 +10022,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10053,10 +10057,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10140,7 +10144,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10175,10 +10179,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10204,10 +10208,10 @@
         <v>82</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>450</v>
@@ -10262,7 +10266,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
